--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/magallanes.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/magallanes.xlsx
@@ -562,7 +562,11 @@
           <t>77.854.171-8</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>77.551.961-4</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/magallanes.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/magallanes.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -702,6 +702,71 @@
         <v>8458.77</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1109692-267-CM26</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>62.000.760-9</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ALIMENTOS SOL DE QUILLOTA SPA</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>77.850.715-3</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>1347.14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
